--- a/Result/profitability/4911.xlsx
+++ b/Result/profitability/4911.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.425</v>
+        <v>0.38</v>
       </c>
       <c r="N2" t="n">
-        <v>77.77</v>
+        <v>76.39375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.37</v>
+        <v>0.3175</v>
       </c>
       <c r="N3" t="n">
-        <v>73.38</v>
+        <v>71.62875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>-0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.30125</v>
+        <v>0.2375</v>
       </c>
       <c r="N4" t="n">
-        <v>70.69875</v>
+        <v>68.88374999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2225</v>
+        <v>0.16</v>
       </c>
       <c r="N5" t="n">
-        <v>68.83125</v>
+        <v>67.00875000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.14625</v>
+        <v>0.08875</v>
       </c>
       <c r="N6" t="n">
-        <v>65.43875</v>
+        <v>63.68875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07375</v>
+        <v>0.03375</v>
       </c>
       <c r="N7" t="n">
-        <v>63.36499999999999</v>
+        <v>61.535</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
         <v>-0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0175</v>
+        <v>0.0025</v>
       </c>
       <c r="N8" t="n">
-        <v>60.56124999999999</v>
+        <v>60.65375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9449,6 +9449,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4911</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>34</v>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>22.98%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" t="n">
+        <v>10</v>
+      </c>
+      <c r="K72" t="n">
+        <v>8</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="N72" t="n">
+        <v>80.9725</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-0.5217391304347827</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0.7399999999999949</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.01057444984281219</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-0.819672131147541</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>-14.58</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>-0.1709261430246189</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
